--- a/InputFiles/GC/TC03_GC_phs001787_ExperimntStratgy-WXS_SampleType-DNA_FileType-BAI.xlsx
+++ b/InputFiles/GC/TC03_GC_phs001787_ExperimntStratgy-WXS_SampleType-DNA_FileType-BAI.xlsx
@@ -536,8 +536,8 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATCH (samp:sample)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
-MATCH (f:file)-[:of_participant]-&gt;(p)
+          <t>MATCH (f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+MATCH (f)-[:from_sample]-&gt;(samp:sample)
 WHERE s.phs_accession = "phs001787"
   AND toLower(f.file_type) = toLower("BAI")
   AND samp.sample_type = "DNA"
@@ -546,8 +546,7 @@
   count(DISTINCT s) AS Studies,
   count(DISTINCT p) AS Participants,
   count(DISTINCT samp) AS Samples,
-  count(DISTINCT f) AS Files
-</t>
+  count(DISTINCT f) AS Files</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -569,8 +568,8 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATCH (samp:sample)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
-MATCH (f:file)-[:of_participant]-&gt;(p)
+          <t>MATCH (f:file)-[:of_participant]-&gt;(p:participant)-[:of_study]-&gt;(s:study)
+MATCH (f)-[:from_sample]-&gt;(samp:sample)
 WHERE s.phs_accession = "phs001787"
   AND toLower(f.file_type) = toLower("BAI")
   AND samp.sample_type = "DNA"
@@ -582,8 +581,7 @@
   COALESCE(samp.sample_name, samp.sample_id) AS sample_name,
   COALESCE(samp.Organization_Name, "Not specified in data") AS organization_name
 ORDER BY samp.sample_id ASC
-LIMIT 100
-</t>
+LIMIT 100</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
